--- a/b_templates/汕仲要素表模板.xlsx
+++ b/b_templates/汕仲要素表模板.xlsx
@@ -7,10 +7,10 @@
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="导出数据" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">导出数据!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>案件号</t>
   </si>
@@ -153,18 +153,6 @@
   </si>
   <si>
     <t>未付租金（官网价1.2倍-优惠金额-已付总租金-履约保证金</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>生日</t>
-  </si>
-  <si>
-    <t>每月还款</t>
-  </si>
-  <si>
-    <t>已付租金+履约保证金</t>
   </si>
 </sst>
 </file>
@@ -355,7 +343,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,18 +353,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,7 +690,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -738,16 +714,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -756,89 +732,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -855,12 +831,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1407,8 +1377,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AO2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelRow="1"/>
+  <dimension ref="A1:AO1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="15.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.875" style="1" customWidth="1"/>
@@ -1552,77 +1522,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" ht="52" customHeight="1" spans="1:41">
-      <c r="A2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL2" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
